--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80ADF08D-899F-8E42-B45C-D78C7309CD8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8DA027-D79D-B041-9105-E00481FC919C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="449">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="456">
   <si>
     <t>Surname</t>
   </si>
@@ -1383,6 +1383,27 @@
   </si>
   <si>
     <t>H264505Y</t>
+  </si>
+  <si>
+    <t>Mutsiki</t>
+  </si>
+  <si>
+    <t>H267821X</t>
+  </si>
+  <si>
+    <t>Muronza</t>
+  </si>
+  <si>
+    <t>H264099K</t>
+  </si>
+  <si>
+    <t>H265496D</t>
+  </si>
+  <si>
+    <t>Zvoushe</t>
+  </si>
+  <si>
+    <t>H267053O</t>
   </si>
 </sst>
 </file>
@@ -2995,6 +3016,9 @@
         <v>0.86</v>
       </c>
       <c r="H69" s="3"/>
+      <c r="J69">
+        <v>0.73</v>
+      </c>
       <c r="M69" s="4"/>
     </row>
     <row r="70" spans="1:13">
@@ -3446,6 +3470,9 @@
       <c r="D99" s="6">
         <v>0.74</v>
       </c>
+      <c r="J99">
+        <v>0.86</v>
+      </c>
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
@@ -3509,26 +3536,29 @@
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
-      <c r="A104" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B104" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C104" s="6" t="s">
+      <c r="A104" s="5" t="s">
+        <v>451</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="C104" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D104" s="6">
+      <c r="D104" s="5">
+        <v>0</v>
+      </c>
+      <c r="J104">
         <v>0.86</v>
       </c>
       <c r="M104" s="4"/>
     </row>
     <row r="105" spans="1:13">
       <c r="A105" s="6" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>159</v>
@@ -3540,760 +3570,769 @@
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D106" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D107" s="6">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="M107" s="4"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D108" s="6">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
+      </c>
+      <c r="J109">
+        <v>0.86</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D111" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D112" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D113" s="6">
-        <v>0.73</v>
+        <v>0.91</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>184</v>
+        <v>222</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>185</v>
+        <v>223</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
-        <v>0.69</v>
+        <v>0.73</v>
       </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
-      <c r="A115" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="C115" s="6" t="s">
+      <c r="A115" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>453</v>
+      </c>
+      <c r="C115" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D115" s="6">
-        <v>0.77</v>
+      <c r="D115" s="5">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0.86</v>
       </c>
       <c r="M115" s="4"/>
     </row>
     <row r="116" spans="1:13">
       <c r="A116" s="6" t="s">
-        <v>220</v>
+        <v>184</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>221</v>
+        <v>185</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D116" s="6">
-        <v>0.68</v>
+        <v>0.69</v>
       </c>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="6" t="s">
-        <v>304</v>
+        <v>198</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>305</v>
+        <v>199</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D117" s="6">
-        <v>0.87</v>
+        <v>0.77</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>271</v>
+        <v>221</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>245</v>
+        <v>159</v>
       </c>
       <c r="D118" s="6">
+        <v>0.68</v>
+      </c>
+      <c r="M118" s="4"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="5" t="s">
+        <v>454</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>455</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D119" s="5">
+        <v>0</v>
+      </c>
+      <c r="J119">
         <v>0.86</v>
-      </c>
-      <c r="M118" s="4"/>
-    </row>
-    <row r="119" spans="1:13">
-      <c r="A119" s="6" t="s">
-        <v>312</v>
-      </c>
-      <c r="B119" s="6" t="s">
-        <v>313</v>
-      </c>
-      <c r="C119" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D119" s="6">
-        <v>0.79</v>
       </c>
       <c r="M119" s="4"/>
     </row>
     <row r="120" spans="1:13">
       <c r="A120" s="6" t="s">
-        <v>334</v>
+        <v>304</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>335</v>
+        <v>305</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D120" s="6">
-        <v>0.64</v>
+        <v>0.87</v>
       </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="6" t="s">
-        <v>328</v>
+        <v>270</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>329</v>
+        <v>271</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D121" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6" t="s">
-        <v>336</v>
+        <v>312</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>337</v>
+        <v>313</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D122" s="6">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6" t="s">
-        <v>258</v>
+        <v>334</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>259</v>
+        <v>335</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D123" s="6">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>266</v>
+        <v>328</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>267</v>
+        <v>329</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D124" s="6">
-        <v>0.88</v>
+        <v>0.79</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>306</v>
+        <v>336</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>307</v>
+        <v>337</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D125" s="6">
-        <v>0.86</v>
+        <v>0.69</v>
       </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6" t="s">
-        <v>290</v>
+        <v>258</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>291</v>
+        <v>259</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D126" s="6">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6" t="s">
-        <v>326</v>
+        <v>266</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>327</v>
+        <v>267</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D127" s="6">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>340</v>
+        <v>306</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>341</v>
+        <v>307</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D128" s="6">
-        <v>0.41</v>
+        <v>0.86</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="6">
-        <v>0.81</v>
+        <v>0.87</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>260</v>
+        <v>326</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>261</v>
+        <v>327</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D130" s="6">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>274</v>
+        <v>340</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>275</v>
+        <v>341</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D131" s="6">
-        <v>0.86</v>
+        <v>0.41</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>316</v>
+        <v>284</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>317</v>
+        <v>285</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D132" s="6">
-        <v>0.87</v>
+        <v>0.81</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>310</v>
+        <v>260</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>311</v>
+        <v>261</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>288</v>
+        <v>274</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>338</v>
+        <v>316</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>339</v>
+        <v>317</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.98</v>
+        <v>0.87</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
       <c r="A136" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D136" s="6">
-        <v>0.75</v>
+        <v>0.8</v>
       </c>
       <c r="M136" s="4"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="6" t="s">
-        <v>330</v>
+        <v>288</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>331</v>
+        <v>289</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D137" s="6">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="6" t="s">
-        <v>246</v>
+        <v>338</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>247</v>
+        <v>339</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D138" s="6">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.71</v>
+        <v>0.75</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6" t="s">
-        <v>262</v>
+        <v>330</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>263</v>
+        <v>331</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="6">
-        <v>0.74</v>
+        <v>0.85</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.88</v>
+        <v>0.71</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>294</v>
+        <v>262</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>295</v>
+        <v>263</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D143" s="6">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="6" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D144" s="6">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6" t="s">
-        <v>280</v>
+        <v>314</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>281</v>
+        <v>315</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="6">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="6" t="s">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>265</v>
+        <v>295</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D146" s="6">
-        <v>0.81</v>
+        <v>0.8</v>
       </c>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.84</v>
+        <v>0.91</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D148" s="6">
-        <v>0.81</v>
+        <v>1</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="6" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D149" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6" t="s">
-        <v>298</v>
+        <v>254</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D150" s="6">
-        <v>0.91</v>
+        <v>0.84</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="6" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D151" s="6">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6" t="s">
-        <v>302</v>
+        <v>252</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>303</v>
+        <v>253</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="6">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>243</v>
+        <v>298</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>244</v>
+        <v>299</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="M153" s="4"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="6" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D154" s="6">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="M154" s="4"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>248</v>
+        <v>302</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>249</v>
+        <v>303</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D155" s="6">
-        <v>0.82</v>
+        <v>0.79</v>
       </c>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="6" t="s">
-        <v>332</v>
+        <v>243</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>333</v>
+        <v>244</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>245</v>
@@ -4305,535 +4344,535 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D157" s="6">
-        <v>0.93</v>
+        <v>0.75</v>
       </c>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6" t="s">
-        <v>278</v>
+        <v>248</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>279</v>
+        <v>249</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="6">
-        <v>1</v>
+        <v>0.82</v>
       </c>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="6" t="s">
-        <v>256</v>
+        <v>332</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>257</v>
+        <v>333</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D159" s="6">
-        <v>0.91</v>
+        <v>0.86</v>
       </c>
       <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="6" t="s">
-        <v>250</v>
+        <v>278</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>251</v>
+        <v>279</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D161" s="6">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D163" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="6" t="s">
-        <v>322</v>
+        <v>250</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>323</v>
+        <v>251</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D164" s="6">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="M164" s="4"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D165" s="6">
-        <v>0.89</v>
+        <v>0.81</v>
       </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6" t="s">
-        <v>349</v>
+        <v>282</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>350</v>
+        <v>283</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D166" s="6">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6" t="s">
-        <v>393</v>
+        <v>322</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>394</v>
+        <v>323</v>
       </c>
       <c r="C167" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D167" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>431</v>
+        <v>318</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>432</v>
+        <v>319</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>366</v>
+        <v>350</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D169" s="6">
-        <v>0.82</v>
+        <v>0.77</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>351</v>
+        <v>393</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>352</v>
+        <v>394</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D170" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="6" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>374</v>
+        <v>432</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D171" s="6">
-        <v>0.98</v>
+        <v>0.74</v>
       </c>
       <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>435</v>
+        <v>365</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>436</v>
+        <v>366</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D172" s="6">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>437</v>
+        <v>351</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>438</v>
+        <v>352</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D173" s="6">
-        <v>0.67</v>
+        <v>0.85</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>419</v>
+        <v>373</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>420</v>
+        <v>374</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D174" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>413</v>
+        <v>435</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>414</v>
+        <v>436</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D175" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6" t="s">
-        <v>377</v>
+        <v>437</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>378</v>
+        <v>438</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D176" s="6">
-        <v>0.84</v>
+        <v>0.67</v>
       </c>
       <c r="M176" s="4"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6" t="s">
-        <v>395</v>
+        <v>419</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>396</v>
+        <v>420</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D177" s="6">
-        <v>0.63</v>
+        <v>0.96</v>
       </c>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D178" s="6">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>398</v>
+        <v>378</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D179" s="6">
-        <v>0.93</v>
+        <v>0.84</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>415</v>
+        <v>395</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>416</v>
+        <v>396</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D180" s="6">
-        <v>0.75</v>
+        <v>0.63</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>361</v>
+        <v>401</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>362</v>
+        <v>402</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D181" s="6">
-        <v>0.96</v>
+        <v>0.82</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>427</v>
+        <v>397</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>428</v>
+        <v>398</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D182" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>368</v>
+        <v>416</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D183" s="6">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>381</v>
+        <v>361</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>382</v>
+        <v>362</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D184" s="6">
-        <v>0.9</v>
+        <v>0.96</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>405</v>
+        <v>427</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>406</v>
+        <v>428</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D185" s="6">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>343</v>
+        <v>368</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D186" s="6">
-        <v>0.76</v>
+        <v>0.81</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>407</v>
+        <v>381</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>408</v>
+        <v>382</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D187" s="6">
-        <v>0.93</v>
+        <v>0.9</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>371</v>
+        <v>405</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D188" s="6">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>447</v>
+        <v>342</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>448</v>
+        <v>343</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D189" s="6">
-        <v>0.81</v>
+        <v>0.76</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>369</v>
+        <v>407</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>370</v>
+        <v>408</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D190" s="6">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>411</v>
+        <v>371</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>412</v>
+        <v>372</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D191" s="6">
-        <v>0.96</v>
+        <v>0.79</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>345</v>
+        <v>447</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>346</v>
+        <v>448</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>344</v>
@@ -4845,235 +4884,241 @@
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>399</v>
+        <v>369</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>400</v>
+        <v>370</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D193" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>375</v>
+        <v>411</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>376</v>
+        <v>412</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D194" s="6">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>389</v>
+        <v>345</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>390</v>
+        <v>346</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D195" s="6">
-        <v>0.77</v>
+        <v>0.81</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D196" s="6">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>421</v>
+        <v>375</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>422</v>
+        <v>376</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D197" s="6">
-        <v>1</v>
+        <v>0.85</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>433</v>
+        <v>389</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>434</v>
+        <v>390</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D198" s="6">
-        <v>0.91</v>
+        <v>0.77</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>357</v>
+        <v>409</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>358</v>
+        <v>410</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D199" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.93</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D200" s="6">
-        <v>0.89</v>
+        <v>1</v>
+      </c>
+      <c r="J200">
+        <v>0.93</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D201" s="6">
-        <v>0.98</v>
+        <v>0.91</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>387</v>
+        <v>357</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>388</v>
+        <v>358</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D202" s="6">
-        <v>0.98</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>403</v>
+        <v>417</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>404</v>
+        <v>418</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D203" s="6">
-        <v>0.96</v>
+        <v>0.89</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>383</v>
+        <v>439</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>384</v>
+        <v>440</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D204" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="A205" s="6" t="s">
-        <v>425</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>426</v>
-      </c>
-      <c r="C205" s="6" t="s">
+      <c r="A205" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C205" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D205" s="6">
-        <v>0.42</v>
+      <c r="D205" s="5">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>0.93</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>441</v>
+        <v>387</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>442</v>
+        <v>388</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D206" s="6">
-        <v>0.88</v>
+        <v>0.98</v>
       </c>
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
       <c r="A207" s="6" t="s">
-        <v>445</v>
+        <v>403</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D207" s="6">
-        <v>0.78</v>
+        <v>0.96</v>
       </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6" t="s">
-        <v>363</v>
+        <v>383</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>344</v>
@@ -5085,180 +5130,224 @@
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>353</v>
+        <v>425</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>354</v>
+        <v>426</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D209" s="6">
-        <v>0.68</v>
+        <v>0.42</v>
+      </c>
+      <c r="J209">
+        <v>0.93</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>391</v>
+        <v>441</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>392</v>
+        <v>442</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D210" s="6">
-        <v>0.76</v>
+        <v>0.88</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>429</v>
+        <v>445</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D211" s="6">
-        <v>0.41</v>
+        <v>0.78</v>
+      </c>
+      <c r="J211">
+        <v>0.93</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>347</v>
+        <v>363</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>348</v>
+        <v>364</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D212" s="6">
-        <v>0.8</v>
+        <v>0.96</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>379</v>
+        <v>353</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>380</v>
+        <v>354</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D213" s="6">
-        <v>0.91</v>
+        <v>0.68</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>423</v>
+        <v>391</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>424</v>
+        <v>392</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D214" s="6">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>359</v>
+        <v>429</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>360</v>
+        <v>430</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D215" s="6">
-        <v>0.95</v>
+        <v>0.41</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>385</v>
+        <v>347</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>386</v>
+        <v>348</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D216" s="6">
-        <v>0.97</v>
+        <v>0.8</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>355</v>
+        <v>379</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>356</v>
+        <v>380</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D217" s="6">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6" t="s">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>444</v>
+        <v>424</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D218" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="M218" s="4"/>
+    </row>
+    <row r="219" spans="1:13">
+      <c r="A219" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="B219" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="C219" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D219" s="6">
+        <v>0.95</v>
+      </c>
+      <c r="J219">
+        <v>0.83</v>
+      </c>
+      <c r="M219" s="4"/>
+    </row>
+    <row r="220" spans="1:13">
+      <c r="A220" s="6" t="s">
+        <v>385</v>
+      </c>
+      <c r="B220" s="6" t="s">
+        <v>386</v>
+      </c>
+      <c r="C220" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D220" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M220" s="4"/>
+    </row>
+    <row r="221" spans="1:13">
+      <c r="A221" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B221" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C221" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D221" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M221" s="4"/>
+    </row>
+    <row r="222" spans="1:13">
+      <c r="A222" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B222" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C222" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D222" s="6">
         <v>0.88</v>
       </c>
-      <c r="M218" s="4"/>
-    </row>
-    <row r="219" spans="1:13">
-      <c r="A219" s="5"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="5"/>
-      <c r="D219" s="5"/>
-      <c r="M219" s="4"/>
-    </row>
-    <row r="220" spans="1:13">
-      <c r="A220" s="5"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="5"/>
-      <c r="D220" s="5"/>
-      <c r="M220" s="4"/>
-    </row>
-    <row r="221" spans="1:13">
-      <c r="A221" s="5"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="5"/>
-      <c r="D221" s="5"/>
-      <c r="M221" s="4"/>
-    </row>
-    <row r="222" spans="1:13">
-      <c r="A222" s="5"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="5"/>
-      <c r="D222" s="5"/>
+      <c r="J222">
+        <v>0.93</v>
+      </c>
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D8DA027-D79D-B041-9105-E00481FC919C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D85BA9C-49CC-A448-A05B-2E6E40008259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="676" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="460">
   <si>
     <t>Surname</t>
   </si>
@@ -1404,6 +1404,18 @@
   </si>
   <si>
     <t>H267053O</t>
+  </si>
+  <si>
+    <t>Muzvazva</t>
+  </si>
+  <si>
+    <t>H267122R</t>
+  </si>
+  <si>
+    <t>Gutsa</t>
+  </si>
+  <si>
+    <t>H268636D</t>
   </si>
 </sst>
 </file>
@@ -2499,6 +2511,9 @@
         <v>0.85</v>
       </c>
       <c r="H36" s="3"/>
+      <c r="J36">
+        <v>0.7</v>
+      </c>
       <c r="M36" s="4"/>
     </row>
     <row r="37" spans="1:13">
@@ -2546,6 +2561,9 @@
         <v>0.86</v>
       </c>
       <c r="H39" s="3"/>
+      <c r="J39">
+        <v>0.7</v>
+      </c>
       <c r="M39" s="4"/>
     </row>
     <row r="40" spans="1:13">
@@ -2578,6 +2596,9 @@
         <v>0.93</v>
       </c>
       <c r="H41" s="3"/>
+      <c r="J41">
+        <v>0.84</v>
+      </c>
       <c r="M41" s="4"/>
     </row>
     <row r="42" spans="1:13">
@@ -2688,6 +2709,9 @@
       <c r="D48" s="6">
         <v>0.79</v>
       </c>
+      <c r="J48">
+        <v>0.84</v>
+      </c>
       <c r="M48" s="4"/>
     </row>
     <row r="49" spans="1:13">
@@ -2844,6 +2868,9 @@
         <v>0.9</v>
       </c>
       <c r="H58" s="3"/>
+      <c r="J58">
+        <v>0.7</v>
+      </c>
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13">
@@ -3049,6 +3076,9 @@
       <c r="D71" s="6">
         <v>0.79</v>
       </c>
+      <c r="J71">
+        <v>0.7</v>
+      </c>
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13">
@@ -4175,6 +4205,9 @@
       <c r="D145" s="6">
         <v>0.88</v>
       </c>
+      <c r="J145">
+        <v>0.83</v>
+      </c>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
@@ -4265,6 +4298,9 @@
       <c r="D151" s="6">
         <v>0.81</v>
       </c>
+      <c r="J151">
+        <v>0.83</v>
+      </c>
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
@@ -4475,6 +4511,9 @@
       <c r="D165" s="6">
         <v>0.81</v>
       </c>
+      <c r="J165">
+        <v>0.83</v>
+      </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
@@ -5351,17 +5390,39 @@
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">
-      <c r="A223" s="5"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="5"/>
-      <c r="D223" s="5"/>
+      <c r="A223" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C223" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D223" s="5">
+        <v>0</v>
+      </c>
+      <c r="J223">
+        <v>0.84</v>
+      </c>
       <c r="M223" s="4"/>
     </row>
     <row r="224" spans="1:13">
-      <c r="A224" s="5"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="5"/>
-      <c r="D224" s="5"/>
+      <c r="A224" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C224" s="5" t="s">
+        <v>245</v>
+      </c>
+      <c r="D224" s="5">
+        <v>0</v>
+      </c>
+      <c r="J224">
+        <v>0.83</v>
+      </c>
       <c r="M224" s="4"/>
     </row>
     <row r="225" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D85BA9C-49CC-A448-A05B-2E6E40008259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780A59E5-D40D-C241-AB97-B816B2AB60E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -2448,6 +2448,9 @@
       <c r="D32" s="6">
         <v>0.95</v>
       </c>
+      <c r="J32">
+        <v>0.78</v>
+      </c>
       <c r="M32" s="4"/>
     </row>
     <row r="33" spans="1:13">
@@ -2824,786 +2827,801 @@
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13">
-      <c r="A56" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="B56" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="D56" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="H56" s="3"/>
+      <c r="A56" s="5" t="s">
+        <v>456</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>457</v>
+      </c>
+      <c r="C56" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D56" s="5">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0.84</v>
+      </c>
       <c r="M56" s="4"/>
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="6" t="s">
-        <v>149</v>
+        <v>66</v>
       </c>
       <c r="B57" s="6" t="s">
-        <v>150</v>
+        <v>67</v>
       </c>
       <c r="C57" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D57" s="6">
-        <v>0.82</v>
-      </c>
+        <v>0.87</v>
+      </c>
+      <c r="H57" s="3"/>
       <c r="M57" s="4"/>
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="6" t="s">
-        <v>82</v>
+        <v>149</v>
       </c>
       <c r="B58" s="6" t="s">
-        <v>83</v>
+        <v>150</v>
       </c>
       <c r="C58" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D58" s="6">
-        <v>0.9</v>
-      </c>
-      <c r="H58" s="3"/>
+        <v>0.82</v>
+      </c>
       <c r="J58">
-        <v>0.7</v>
+        <v>0.78</v>
       </c>
       <c r="M58" s="4"/>
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="6" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D59" s="6">
-        <v>0.86</v>
+        <v>0.9</v>
       </c>
       <c r="H59" s="3"/>
+      <c r="J59">
+        <v>0.7</v>
+      </c>
       <c r="M59" s="4"/>
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D60" s="6">
-        <v>0.96</v>
+        <v>0.86</v>
       </c>
       <c r="H60" s="3"/>
       <c r="M60" s="4"/>
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="6" t="s">
-        <v>123</v>
+        <v>62</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="C61" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D61" s="6">
-        <v>0.78</v>
-      </c>
+        <v>0.96</v>
+      </c>
+      <c r="H61" s="3"/>
       <c r="M61" s="4"/>
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="6" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="B62" s="6" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="C62" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D62" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="H62" s="3"/>
+        <v>0.78</v>
+      </c>
       <c r="M62" s="4"/>
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="6" t="s">
-        <v>119</v>
+        <v>86</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>120</v>
+        <v>87</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D63" s="6">
-        <v>0.9</v>
-      </c>
+        <v>0.95</v>
+      </c>
+      <c r="H63" s="3"/>
       <c r="M63" s="4"/>
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="6" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D64" s="6">
-        <v>0.75</v>
+        <v>0.9</v>
       </c>
       <c r="M64" s="4"/>
     </row>
     <row r="65" spans="1:13">
       <c r="A65" s="6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D65" s="6">
-        <v>0.56999999999999995</v>
+        <v>0.75</v>
+      </c>
+      <c r="J65">
+        <v>0.78</v>
       </c>
       <c r="M65" s="4"/>
     </row>
     <row r="66" spans="1:13">
       <c r="A66" s="6" t="s">
-        <v>34</v>
+        <v>145</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D66" s="6">
-        <v>0.75</v>
-      </c>
-      <c r="H66" s="3"/>
+        <v>0.56999999999999995</v>
+      </c>
       <c r="M66" s="4"/>
     </row>
     <row r="67" spans="1:13">
       <c r="A67" s="6" t="s">
-        <v>99</v>
+        <v>34</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>100</v>
+        <v>35</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D67" s="6">
-        <v>0.77</v>
+        <v>0.75</v>
       </c>
       <c r="H67" s="3"/>
       <c r="M67" s="4"/>
     </row>
     <row r="68" spans="1:13">
       <c r="A68" s="6" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D68" s="6">
-        <v>0.88</v>
+        <v>0.77</v>
       </c>
       <c r="H68" s="3"/>
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="1:13">
       <c r="A69" s="6" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>25</v>
+        <v>104</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D69" s="6">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="H69" s="3"/>
       <c r="J69">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="M69" s="4"/>
     </row>
     <row r="70" spans="1:13">
       <c r="A70" s="6" t="s">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>79</v>
+        <v>25</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D70" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
+      </c>
+      <c r="H70" s="3"/>
+      <c r="J70">
+        <v>0.73</v>
       </c>
       <c r="M70" s="4"/>
     </row>
     <row r="71" spans="1:13">
       <c r="A71" s="6" t="s">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>128</v>
+        <v>79</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D71" s="6">
-        <v>0.79</v>
-      </c>
-      <c r="J71">
-        <v>0.7</v>
+        <v>0.88</v>
       </c>
       <c r="M71" s="4"/>
     </row>
     <row r="72" spans="1:13">
       <c r="A72" s="6" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D72" s="6">
-        <v>0.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="J72">
+        <v>0.7</v>
       </c>
       <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13">
       <c r="A73" s="6" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>51</v>
+        <v>122</v>
       </c>
       <c r="C73" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D73" s="6">
-        <v>0.98</v>
-      </c>
-      <c r="H73" s="3"/>
+        <v>0.88</v>
+      </c>
+      <c r="J73">
+        <v>0.78</v>
+      </c>
       <c r="M73" s="4"/>
     </row>
     <row r="74" spans="1:13">
       <c r="A74" s="6" t="s">
-        <v>212</v>
+        <v>50</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>213</v>
+        <v>51</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>159</v>
+        <v>15</v>
       </c>
       <c r="D74" s="6">
-        <v>0.93</v>
-      </c>
+        <v>0.98</v>
+      </c>
+      <c r="H74" s="3"/>
       <c r="M74" s="4"/>
     </row>
     <row r="75" spans="1:13">
       <c r="A75" s="6" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="C75" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D75" s="6">
-        <v>0.73</v>
+        <v>0.93</v>
       </c>
       <c r="M75" s="4"/>
     </row>
     <row r="76" spans="1:13">
       <c r="A76" s="6" t="s">
-        <v>178</v>
+        <v>210</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="C76" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D76" s="6">
-        <v>0.91</v>
+        <v>0.73</v>
       </c>
       <c r="M76" s="4"/>
     </row>
     <row r="77" spans="1:13">
       <c r="A77" s="6" t="s">
-        <v>224</v>
+        <v>178</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D77" s="6">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="M77" s="4"/>
     </row>
     <row r="78" spans="1:13">
       <c r="A78" s="6" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D78" s="6">
-        <v>0.85</v>
+        <v>0.88</v>
       </c>
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
       <c r="A79" s="6" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D79" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="6" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D80" s="6">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="6" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D81" s="6">
-        <v>0.84</v>
+        <v>0.82</v>
       </c>
       <c r="M81" s="4"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D82" s="6">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D83" s="6">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="6" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="6">
-        <v>0.78</v>
+        <v>0.53</v>
       </c>
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="6" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D85" s="6">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="6" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D86" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D87" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="6" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D88" s="6">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D89" s="6">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D90" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D91" s="6">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D92" s="6">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D93" s="6">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D94" s="6">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D95" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="6" t="s">
-        <v>241</v>
+        <v>166</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D96" s="6">
-        <v>0.69</v>
+        <v>0.92</v>
       </c>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="6" t="s">
-        <v>13</v>
+        <v>241</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D97" s="6">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="6" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D98" s="6">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D99" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="J99">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="6" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D100" s="6">
-        <v>0.63</v>
+        <v>0.74</v>
+      </c>
+      <c r="J100">
+        <v>0.86</v>
       </c>
       <c r="M100" s="4"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D101" s="6">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D102" s="6">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D103" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="M103" s="4"/>
+    </row>
+    <row r="104" spans="1:13">
+      <c r="A104" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B104" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C104" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D104" s="6">
         <v>0.91</v>
       </c>
-      <c r="M103" s="4"/>
-    </row>
-    <row r="104" spans="1:13">
-      <c r="A104" s="5" t="s">
+      <c r="M104" s="4"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B105" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C105" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D104" s="5">
+      <c r="D105" s="5">
         <v>0</v>
       </c>
-      <c r="J104">
-        <v>0.86</v>
-      </c>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="A105" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B105" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C105" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D105" s="6">
+      <c r="J105">
         <v>0.86</v>
       </c>
       <c r="M105" s="4"/>
     </row>
     <row r="106" spans="1:13">
       <c r="A106" s="6" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>159</v>
@@ -3615,682 +3633,691 @@
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D107" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="M107" s="4"/>
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D108" s="6">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="J109">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
+      </c>
+      <c r="J110">
+        <v>0.86</v>
       </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D111" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D112" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D113" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="M114" s="4"/>
+    </row>
+    <row r="115" spans="1:13">
+      <c r="A115" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D115" s="6">
         <v>0.73</v>
       </c>
-      <c r="M114" s="4"/>
-    </row>
-    <row r="115" spans="1:13">
-      <c r="A115" s="5" t="s">
+      <c r="M115" s="4"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B116" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="C115" s="5" t="s">
+      <c r="C116" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D115" s="5">
+      <c r="D116" s="5">
         <v>0</v>
       </c>
-      <c r="J115">
+      <c r="J116">
         <v>0.86</v>
-      </c>
-      <c r="M115" s="4"/>
-    </row>
-    <row r="116" spans="1:13">
-      <c r="A116" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B116" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D116" s="6">
-        <v>0.69</v>
       </c>
       <c r="M116" s="4"/>
     </row>
     <row r="117" spans="1:13">
       <c r="A117" s="6" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D117" s="6">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D118" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M118" s="4"/>
+    </row>
+    <row r="119" spans="1:13">
+      <c r="A119" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C119" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D119" s="6">
         <v>0.68</v>
       </c>
-      <c r="M118" s="4"/>
-    </row>
-    <row r="119" spans="1:13">
-      <c r="A119" s="5" t="s">
+      <c r="M119" s="4"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B120" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C119" s="5" t="s">
+      <c r="C120" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D119" s="5">
+      <c r="D120" s="5">
         <v>0</v>
       </c>
-      <c r="J119">
+      <c r="J120">
         <v>0.86</v>
-      </c>
-      <c r="M119" s="4"/>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="A120" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="B120" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C120" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D120" s="6">
-        <v>0.87</v>
       </c>
       <c r="M120" s="4"/>
     </row>
     <row r="121" spans="1:13">
       <c r="A121" s="6" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D121" s="6">
-        <v>0.86</v>
+        <v>0.87</v>
+      </c>
+      <c r="J121">
+        <v>0.8</v>
       </c>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D122" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D123" s="6">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D124" s="6">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D125" s="6">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D126" s="6">
-        <v>0.91</v>
+        <v>0.69</v>
       </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D127" s="6">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D128" s="6">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D130" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="J130">
         <v>0.8</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D131" s="6">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D132" s="6">
-        <v>0.81</v>
+        <v>0.41</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.86</v>
+        <v>0.71</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>316</v>
+        <v>274</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>317</v>
+        <v>275</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="M135" s="4"/>
     </row>
     <row r="136" spans="1:13">
-      <c r="A136" s="6" t="s">
-        <v>310</v>
-      </c>
-      <c r="B136" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="C136" s="6" t="s">
+      <c r="A136" s="5" t="s">
+        <v>458</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>459</v>
+      </c>
+      <c r="C136" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D136" s="6">
-        <v>0.8</v>
+      <c r="D136" s="5">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>0.83</v>
       </c>
       <c r="M136" s="4"/>
     </row>
     <row r="137" spans="1:13">
       <c r="A137" s="6" t="s">
-        <v>288</v>
+        <v>316</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>289</v>
+        <v>317</v>
       </c>
       <c r="C137" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D137" s="6">
-        <v>0.88</v>
+        <v>0.87</v>
       </c>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="6" t="s">
-        <v>338</v>
+        <v>310</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>339</v>
+        <v>311</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D138" s="6">
-        <v>0.98</v>
+        <v>0.8</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>308</v>
+        <v>288</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>309</v>
+        <v>289</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="6">
-        <v>0.85</v>
+        <v>0.98</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>246</v>
+        <v>308</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>247</v>
+        <v>309</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.88</v>
+        <v>0.75</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.71</v>
+        <v>0.85</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>262</v>
+        <v>246</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>263</v>
+        <v>247</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D143" s="6">
-        <v>0.74</v>
+        <v>0.88</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="6" t="s">
-        <v>268</v>
+        <v>324</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>269</v>
+        <v>325</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D144" s="6">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6" t="s">
-        <v>314</v>
+        <v>262</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>315</v>
+        <v>263</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="J145">
-        <v>0.83</v>
+        <v>0.74</v>
       </c>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="6" t="s">
-        <v>294</v>
+        <v>268</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>295</v>
+        <v>269</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D146" s="6">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>272</v>
+        <v>314</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>273</v>
+        <v>315</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.91</v>
+        <v>0.88</v>
+      </c>
+      <c r="J147">
+        <v>0.83</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D148" s="6">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="6" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D149" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6" t="s">
-        <v>254</v>
+        <v>280</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>255</v>
+        <v>281</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D150" s="6">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="6" t="s">
-        <v>286</v>
+        <v>264</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>287</v>
+        <v>265</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>245</v>
@@ -4298,77 +4325,77 @@
       <c r="D151" s="6">
         <v>0.81</v>
       </c>
-      <c r="J151">
-        <v>0.83</v>
-      </c>
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="6">
-        <v>0.85</v>
+        <v>0.84</v>
       </c>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>298</v>
+        <v>286</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>299</v>
+        <v>287</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
-        <v>0.91</v>
+        <v>0.81</v>
+      </c>
+      <c r="J153">
+        <v>0.83</v>
       </c>
       <c r="M153" s="4"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="6" t="s">
-        <v>296</v>
+        <v>252</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>297</v>
+        <v>253</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D154" s="6">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="M154" s="4"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D155" s="6">
-        <v>0.79</v>
+        <v>0.91</v>
       </c>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="6" t="s">
-        <v>243</v>
+        <v>296</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>244</v>
+        <v>297</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>245</v>
@@ -4380,130 +4407,133 @@
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D157" s="6">
-        <v>0.75</v>
+        <v>0.79</v>
       </c>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="6">
-        <v>0.82</v>
+        <v>0.86</v>
       </c>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="6" t="s">
-        <v>332</v>
+        <v>300</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>333</v>
+        <v>301</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D159" s="6">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>292</v>
+        <v>248</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="6" t="s">
-        <v>278</v>
+        <v>332</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>279</v>
+        <v>333</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D161" s="6">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>256</v>
+        <v>292</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>257</v>
+        <v>293</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D163" s="6">
-        <v>0.81</v>
+        <v>1</v>
       </c>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="6" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D164" s="6">
-        <v>0.93</v>
+        <v>0.91</v>
+      </c>
+      <c r="J164">
+        <v>0.8</v>
       </c>
       <c r="M164" s="4"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6" t="s">
-        <v>320</v>
+        <v>276</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>245</v>
@@ -4511,467 +4541,467 @@
       <c r="D165" s="6">
         <v>0.81</v>
       </c>
-      <c r="J165">
-        <v>0.83</v>
-      </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6" t="s">
-        <v>282</v>
+        <v>250</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>283</v>
+        <v>251</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D166" s="6">
-        <v>0.8</v>
+        <v>0.93</v>
       </c>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D167" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
+      </c>
+      <c r="J167">
+        <v>0.83</v>
       </c>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>318</v>
+        <v>282</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>319</v>
+        <v>283</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>349</v>
+        <v>322</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>350</v>
+        <v>323</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D169" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>393</v>
+        <v>318</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>394</v>
+        <v>319</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.8</v>
+        <v>0.89</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="6" t="s">
-        <v>431</v>
+        <v>349</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>432</v>
+        <v>350</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D171" s="6">
-        <v>0.74</v>
+        <v>0.77</v>
       </c>
       <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>365</v>
+        <v>393</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>366</v>
+        <v>394</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D172" s="6">
-        <v>0.82</v>
+        <v>0.8</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>351</v>
+        <v>431</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>352</v>
+        <v>432</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D173" s="6">
-        <v>0.85</v>
+        <v>0.74</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D174" s="6">
-        <v>0.98</v>
+        <v>0.82</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>435</v>
+        <v>351</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>436</v>
+        <v>352</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D175" s="6">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6" t="s">
-        <v>437</v>
+        <v>373</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>438</v>
+        <v>374</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D176" s="6">
-        <v>0.67</v>
+        <v>0.98</v>
       </c>
       <c r="M176" s="4"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6" t="s">
-        <v>419</v>
+        <v>435</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>420</v>
+        <v>436</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D177" s="6">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>413</v>
+        <v>437</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>414</v>
+        <v>438</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D178" s="6">
-        <v>0.92</v>
+        <v>0.67</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>378</v>
+        <v>420</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D179" s="6">
-        <v>0.84</v>
+        <v>0.96</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>395</v>
+        <v>413</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>396</v>
+        <v>414</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D180" s="6">
-        <v>0.63</v>
+        <v>0.92</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>401</v>
+        <v>377</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>402</v>
+        <v>378</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D181" s="6">
-        <v>0.82</v>
+        <v>0.84</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D182" s="6">
-        <v>0.93</v>
+        <v>0.63</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>415</v>
+        <v>401</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>416</v>
+        <v>402</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D183" s="6">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>361</v>
+        <v>397</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>362</v>
+        <v>398</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D184" s="6">
-        <v>0.96</v>
+        <v>0.93</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>427</v>
+        <v>415</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>428</v>
+        <v>416</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D185" s="6">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D186" s="6">
-        <v>0.81</v>
+        <v>0.96</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>381</v>
+        <v>427</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>382</v>
+        <v>428</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D187" s="6">
-        <v>0.9</v>
+        <v>0.92</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>405</v>
+        <v>367</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>406</v>
+        <v>368</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D188" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>342</v>
+        <v>381</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>343</v>
+        <v>382</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D189" s="6">
-        <v>0.76</v>
+        <v>0.9</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D190" s="6">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D191" s="6">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>447</v>
+        <v>407</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>448</v>
+        <v>408</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D192" s="6">
-        <v>0.81</v>
+        <v>0.93</v>
       </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D193" s="6">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>411</v>
+        <v>447</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>412</v>
+        <v>448</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D194" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>345</v>
+        <v>369</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>346</v>
+        <v>370</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D195" s="6">
-        <v>0.81</v>
+        <v>0.85</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>344</v>
@@ -4983,151 +5013,151 @@
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>376</v>
+        <v>346</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D197" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
+      </c>
+      <c r="J197">
+        <v>0.79</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D198" s="6">
-        <v>0.77</v>
+        <v>0.96</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>409</v>
+        <v>375</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>410</v>
+        <v>376</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D199" s="6">
-        <v>0.93</v>
+        <v>0.85</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>421</v>
+        <v>389</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>422</v>
+        <v>390</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D200" s="6">
-        <v>1</v>
-      </c>
-      <c r="J200">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>433</v>
+        <v>409</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>434</v>
+        <v>410</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D201" s="6">
-        <v>0.91</v>
+        <v>0.93</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>357</v>
+        <v>421</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>358</v>
+        <v>422</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D202" s="6">
-        <v>0.55000000000000004</v>
+        <v>1</v>
+      </c>
+      <c r="J202">
+        <v>0.93</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>417</v>
+        <v>433</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>418</v>
+        <v>434</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D203" s="6">
-        <v>0.89</v>
+        <v>0.91</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>439</v>
+        <v>357</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>440</v>
+        <v>358</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D204" s="6">
-        <v>0.98</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
-      <c r="A205" s="5" t="s">
-        <v>449</v>
-      </c>
-      <c r="B205" s="5" t="s">
-        <v>450</v>
-      </c>
-      <c r="C205" s="5" t="s">
+      <c r="A205" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="B205" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="C205" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="D205" s="5">
-        <v>0</v>
-      </c>
-      <c r="J205">
-        <v>0.93</v>
+      <c r="D205" s="6">
+        <v>0.89</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>387</v>
+        <v>439</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>388</v>
+        <v>440</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>344</v>
@@ -5138,80 +5168,80 @@
       <c r="M206" s="4"/>
     </row>
     <row r="207" spans="1:13">
-      <c r="A207" s="6" t="s">
-        <v>403</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>404</v>
-      </c>
-      <c r="C207" s="6" t="s">
+      <c r="A207" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>450</v>
+      </c>
+      <c r="C207" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D207" s="6">
-        <v>0.96</v>
+      <c r="D207" s="5">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>0.93</v>
       </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
       <c r="A208" s="6" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D208" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>425</v>
+        <v>403</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>426</v>
+        <v>404</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D209" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="J209">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>441</v>
+        <v>383</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>442</v>
+        <v>384</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D210" s="6">
-        <v>0.88</v>
+        <v>0.96</v>
       </c>
       <c r="M210" s="4"/>
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>445</v>
+        <v>425</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>446</v>
+        <v>426</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D211" s="6">
-        <v>0.78</v>
+        <v>0.42</v>
       </c>
       <c r="J211">
         <v>0.93</v>
@@ -5220,208 +5250,205 @@
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>363</v>
+        <v>441</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>364</v>
+        <v>442</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D212" s="6">
-        <v>0.96</v>
+        <v>0.88</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>353</v>
+        <v>445</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>354</v>
+        <v>446</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D213" s="6">
-        <v>0.68</v>
+        <v>0.78</v>
+      </c>
+      <c r="J213">
+        <v>0.93</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>391</v>
+        <v>363</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D214" s="6">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>429</v>
+        <v>353</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>430</v>
+        <v>354</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D215" s="6">
-        <v>0.41</v>
+        <v>0.68</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>347</v>
+        <v>391</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>348</v>
+        <v>392</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D216" s="6">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>379</v>
+        <v>429</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>380</v>
+        <v>430</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D217" s="6">
-        <v>0.91</v>
+        <v>0.41</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6" t="s">
-        <v>423</v>
+        <v>347</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>424</v>
+        <v>348</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D218" s="6">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>359</v>
+        <v>379</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>360</v>
+        <v>380</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D219" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="J219">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>385</v>
+        <v>423</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>386</v>
+        <v>424</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D220" s="6">
-        <v>0.97</v>
+        <v>0.91</v>
       </c>
       <c r="M220" s="4"/>
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D221" s="6">
-        <v>0.97</v>
+        <v>0.95</v>
+      </c>
+      <c r="J221">
+        <v>0.83</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>443</v>
+        <v>385</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>444</v>
+        <v>386</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D222" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M222" s="4"/>
+    </row>
+    <row r="223" spans="1:13">
+      <c r="A223" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="B223" s="6" t="s">
+        <v>356</v>
+      </c>
+      <c r="C223" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D223" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M223" s="4"/>
+    </row>
+    <row r="224" spans="1:13">
+      <c r="A224" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B224" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C224" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D224" s="6">
         <v>0.88</v>
       </c>
-      <c r="J222">
+      <c r="J224">
         <v>0.93</v>
-      </c>
-      <c r="M222" s="4"/>
-    </row>
-    <row r="223" spans="1:13">
-      <c r="A223" s="5" t="s">
-        <v>456</v>
-      </c>
-      <c r="B223" s="5" t="s">
-        <v>457</v>
-      </c>
-      <c r="C223" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D223" s="5">
-        <v>0</v>
-      </c>
-      <c r="J223">
-        <v>0.84</v>
-      </c>
-      <c r="M223" s="4"/>
-    </row>
-    <row r="224" spans="1:13">
-      <c r="A224" s="5" t="s">
-        <v>458</v>
-      </c>
-      <c r="B224" s="5" t="s">
-        <v>459</v>
-      </c>
-      <c r="C224" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="D224" s="5">
-        <v>0</v>
-      </c>
-      <c r="J224">
-        <v>0.83</v>
       </c>
       <c r="M224" s="4"/>
     </row>

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{780A59E5-D40D-C241-AB97-B816B2AB60E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E851313-6201-9249-9F5C-94CC154F5682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="685" uniqueCount="462">
   <si>
     <t>Surname</t>
   </si>
@@ -1416,6 +1416,12 @@
   </si>
   <si>
     <t>H268636D</t>
+  </si>
+  <si>
+    <t>Chihwayi</t>
+  </si>
+  <si>
+    <t>H263423S</t>
   </si>
 </sst>
 </file>
@@ -1975,6 +1981,9 @@
         <v>0.73</v>
       </c>
       <c r="H2" s="3"/>
+      <c r="J2">
+        <v>0.72</v>
+      </c>
       <c r="M2" s="7"/>
     </row>
     <row r="3" spans="1:13">
@@ -1991,6 +2000,9 @@
         <v>0.79</v>
       </c>
       <c r="H3" s="3"/>
+      <c r="J3">
+        <v>0.72</v>
+      </c>
       <c r="M3" s="7"/>
     </row>
     <row r="4" spans="1:13">
@@ -2824,6 +2836,9 @@
         <v>0.88</v>
       </c>
       <c r="H55" s="3"/>
+      <c r="J55">
+        <v>0.72</v>
+      </c>
       <c r="M55" s="4"/>
     </row>
     <row r="56" spans="1:13">
@@ -3022,6 +3037,9 @@
         <v>0.75</v>
       </c>
       <c r="H67" s="3"/>
+      <c r="J67">
+        <v>0.72</v>
+      </c>
       <c r="M67" s="4"/>
     </row>
     <row r="68" spans="1:13">
@@ -3038,6 +3056,9 @@
         <v>0.77</v>
       </c>
       <c r="H68" s="3"/>
+      <c r="J68">
+        <v>0.72</v>
+      </c>
       <c r="M68" s="4"/>
     </row>
     <row r="69" spans="1:13">
@@ -3158,6 +3179,9 @@
       <c r="D75" s="6">
         <v>0.93</v>
       </c>
+      <c r="J75">
+        <v>0.78</v>
+      </c>
       <c r="M75" s="4"/>
     </row>
     <row r="76" spans="1:13">
@@ -3206,437 +3230,446 @@
       <c r="M78" s="4"/>
     </row>
     <row r="79" spans="1:13">
-      <c r="A79" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="B79" s="6" t="s">
-        <v>219</v>
-      </c>
-      <c r="C79" s="6" t="s">
+      <c r="A79" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>461</v>
+      </c>
+      <c r="C79" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D79" s="6">
-        <v>0.85</v>
+      <c r="D79" s="5">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>0.78</v>
       </c>
       <c r="M79" s="4"/>
     </row>
     <row r="80" spans="1:13">
       <c r="A80" s="6" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D80" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="M80" s="4"/>
     </row>
     <row r="81" spans="1:13">
       <c r="A81" s="6" t="s">
-        <v>168</v>
+        <v>233</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>169</v>
+        <v>234</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D81" s="6">
-        <v>0.82</v>
+        <v>0.96</v>
       </c>
       <c r="M81" s="4"/>
     </row>
     <row r="82" spans="1:13">
       <c r="A82" s="6" t="s">
-        <v>202</v>
+        <v>168</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>203</v>
+        <v>169</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D82" s="6">
-        <v>0.84</v>
+        <v>0.82</v>
+      </c>
+      <c r="J82">
+        <v>0.78</v>
       </c>
       <c r="M82" s="4"/>
     </row>
     <row r="83" spans="1:13">
       <c r="A83" s="6" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D83" s="6">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="M83" s="4"/>
     </row>
     <row r="84" spans="1:13">
       <c r="A84" s="6" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D84" s="6">
-        <v>0.53</v>
+        <v>0.88</v>
       </c>
       <c r="M84" s="4"/>
     </row>
     <row r="85" spans="1:13">
       <c r="A85" s="6" t="s">
-        <v>229</v>
+        <v>208</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D85" s="6">
-        <v>0.78</v>
+        <v>0.53</v>
       </c>
       <c r="M85" s="4"/>
     </row>
     <row r="86" spans="1:13">
       <c r="A86" s="6" t="s">
-        <v>186</v>
+        <v>229</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>187</v>
+        <v>230</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D86" s="6">
-        <v>0.91</v>
+        <v>0.78</v>
       </c>
       <c r="M86" s="4"/>
     </row>
     <row r="87" spans="1:13">
       <c r="A87" s="6" t="s">
-        <v>160</v>
+        <v>186</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>161</v>
+        <v>187</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D87" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
       </c>
       <c r="M87" s="4"/>
     </row>
     <row r="88" spans="1:13">
       <c r="A88" s="6" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>183</v>
+        <v>161</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D88" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="M88" s="4"/>
     </row>
     <row r="89" spans="1:13">
       <c r="A89" s="6" t="s">
-        <v>227</v>
+        <v>182</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>228</v>
+        <v>183</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D89" s="6">
-        <v>0.78</v>
+        <v>0.8</v>
       </c>
       <c r="M89" s="4"/>
     </row>
     <row r="90" spans="1:13">
       <c r="A90" s="6" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>207</v>
+        <v>228</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D90" s="6">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="M90" s="4"/>
     </row>
     <row r="91" spans="1:13">
       <c r="A91" s="6" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D91" s="6">
-        <v>0.8</v>
+        <v>0.85</v>
       </c>
       <c r="M91" s="4"/>
     </row>
     <row r="92" spans="1:13">
       <c r="A92" s="6" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D92" s="6">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="M92" s="4"/>
     </row>
     <row r="93" spans="1:13">
       <c r="A93" s="6" t="s">
-        <v>164</v>
+        <v>188</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>165</v>
+        <v>189</v>
       </c>
       <c r="C93" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D93" s="6">
-        <v>0.78</v>
+        <v>0.92</v>
       </c>
       <c r="M93" s="4"/>
     </row>
     <row r="94" spans="1:13">
       <c r="A94" s="6" t="s">
-        <v>239</v>
+        <v>164</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>240</v>
+        <v>165</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D94" s="6">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="M94" s="4"/>
     </row>
     <row r="95" spans="1:13">
       <c r="A95" s="6" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D95" s="6">
-        <v>0.93</v>
+        <v>0.73</v>
       </c>
       <c r="M95" s="4"/>
     </row>
     <row r="96" spans="1:13">
       <c r="A96" s="6" t="s">
-        <v>166</v>
+        <v>216</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>167</v>
+        <v>217</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D96" s="6">
-        <v>0.92</v>
+        <v>0.93</v>
+      </c>
+      <c r="J96">
+        <v>0.78</v>
       </c>
       <c r="M96" s="4"/>
     </row>
     <row r="97" spans="1:13">
       <c r="A97" s="6" t="s">
-        <v>241</v>
+        <v>166</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>242</v>
+        <v>167</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D97" s="6">
-        <v>0.69</v>
+        <v>0.92</v>
       </c>
       <c r="M97" s="4"/>
     </row>
     <row r="98" spans="1:13">
       <c r="A98" s="6" t="s">
-        <v>13</v>
+        <v>241</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D98" s="6">
-        <v>0.74</v>
+        <v>0.69</v>
       </c>
       <c r="M98" s="4"/>
     </row>
     <row r="99" spans="1:13">
       <c r="A99" s="6" t="s">
-        <v>200</v>
+        <v>13</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D99" s="6">
-        <v>0.81</v>
+        <v>0.74</v>
       </c>
       <c r="M99" s="4"/>
     </row>
     <row r="100" spans="1:13">
       <c r="A100" s="6" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D100" s="6">
-        <v>0.74</v>
-      </c>
-      <c r="J100">
-        <v>0.86</v>
+        <v>0.81</v>
       </c>
       <c r="M100" s="4"/>
     </row>
     <row r="101" spans="1:13">
       <c r="A101" s="6" t="s">
-        <v>157</v>
+        <v>194</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>158</v>
+        <v>195</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D101" s="6">
-        <v>0.63</v>
+        <v>0.74</v>
+      </c>
+      <c r="J101">
+        <v>0.86</v>
       </c>
       <c r="M101" s="4"/>
     </row>
     <row r="102" spans="1:13">
       <c r="A102" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D102" s="6">
-        <v>0.98</v>
+        <v>0.63</v>
       </c>
       <c r="M102" s="4"/>
     </row>
     <row r="103" spans="1:13">
       <c r="A103" s="6" t="s">
-        <v>176</v>
+        <v>162</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D103" s="6">
-        <v>0.73</v>
+        <v>0.98</v>
       </c>
       <c r="M103" s="4"/>
     </row>
     <row r="104" spans="1:13">
       <c r="A104" s="6" t="s">
-        <v>190</v>
+        <v>176</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D104" s="6">
+        <v>0.73</v>
+      </c>
+      <c r="M104" s="4"/>
+    </row>
+    <row r="105" spans="1:13">
+      <c r="A105" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B105" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="C105" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D105" s="6">
         <v>0.91</v>
       </c>
-      <c r="M104" s="4"/>
-    </row>
-    <row r="105" spans="1:13">
-      <c r="A105" s="5" t="s">
+      <c r="M105" s="4"/>
+    </row>
+    <row r="106" spans="1:13">
+      <c r="A106" s="5" t="s">
         <v>451</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B106" s="5" t="s">
         <v>452</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C106" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D105" s="5">
+      <c r="D106" s="5">
         <v>0</v>
       </c>
-      <c r="J105">
-        <v>0.86</v>
-      </c>
-      <c r="M105" s="4"/>
-    </row>
-    <row r="106" spans="1:13">
-      <c r="A106" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="B106" s="6" t="s">
-        <v>232</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D106" s="6">
+      <c r="J106">
         <v>0.86</v>
       </c>
       <c r="M106" s="4"/>
     </row>
     <row r="107" spans="1:13">
       <c r="A107" s="6" t="s">
-        <v>170</v>
+        <v>231</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>171</v>
+        <v>232</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>159</v>
@@ -3648,1579 +3681,1582 @@
     </row>
     <row r="108" spans="1:13">
       <c r="A108" s="6" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D108" s="6">
-        <v>0.87</v>
+        <v>0.86</v>
       </c>
       <c r="M108" s="4"/>
     </row>
     <row r="109" spans="1:13">
       <c r="A109" s="6" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D109" s="6">
-        <v>0.89</v>
+        <v>0.87</v>
       </c>
       <c r="M109" s="4"/>
     </row>
     <row r="110" spans="1:13">
       <c r="A110" s="6" t="s">
-        <v>235</v>
+        <v>180</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>236</v>
+        <v>181</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D110" s="6">
-        <v>0.86</v>
-      </c>
-      <c r="J110">
-        <v>0.86</v>
+        <v>0.89</v>
       </c>
       <c r="M110" s="4"/>
     </row>
     <row r="111" spans="1:13">
       <c r="A111" s="6" t="s">
-        <v>174</v>
+        <v>235</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>175</v>
+        <v>236</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D111" s="6">
-        <v>0.88</v>
+        <v>0.86</v>
+      </c>
+      <c r="J111">
+        <v>0.86</v>
       </c>
       <c r="M111" s="4"/>
     </row>
     <row r="112" spans="1:13">
       <c r="A112" s="6" t="s">
-        <v>192</v>
+        <v>174</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>193</v>
+        <v>175</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D112" s="6">
-        <v>0.75</v>
+        <v>0.88</v>
+      </c>
+      <c r="J112">
+        <v>0.78</v>
       </c>
       <c r="M112" s="4"/>
     </row>
     <row r="113" spans="1:13">
       <c r="A113" s="6" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D113" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="M113" s="4"/>
     </row>
     <row r="114" spans="1:13">
       <c r="A114" s="6" t="s">
-        <v>237</v>
+        <v>196</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>238</v>
+        <v>197</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D114" s="6">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="M114" s="4"/>
     </row>
     <row r="115" spans="1:13">
       <c r="A115" s="6" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D115" s="6">
+        <v>0.91</v>
+      </c>
+      <c r="M115" s="4"/>
+    </row>
+    <row r="116" spans="1:13">
+      <c r="A116" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="B116" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D116" s="6">
         <v>0.73</v>
       </c>
-      <c r="M115" s="4"/>
-    </row>
-    <row r="116" spans="1:13">
-      <c r="A116" s="5" t="s">
+      <c r="M116" s="4"/>
+    </row>
+    <row r="117" spans="1:13">
+      <c r="A117" s="5" t="s">
         <v>423</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B117" s="5" t="s">
         <v>453</v>
       </c>
-      <c r="C116" s="5" t="s">
+      <c r="C117" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D116" s="5">
+      <c r="D117" s="5">
         <v>0</v>
       </c>
-      <c r="J116">
+      <c r="J117">
         <v>0.86</v>
-      </c>
-      <c r="M116" s="4"/>
-    </row>
-    <row r="117" spans="1:13">
-      <c r="A117" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="B117" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="C117" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="D117" s="6">
-        <v>0.69</v>
       </c>
       <c r="M117" s="4"/>
     </row>
     <row r="118" spans="1:13">
       <c r="A118" s="6" t="s">
-        <v>198</v>
+        <v>184</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D118" s="6">
-        <v>0.77</v>
+        <v>0.69</v>
       </c>
       <c r="M118" s="4"/>
     </row>
     <row r="119" spans="1:13">
       <c r="A119" s="6" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>221</v>
+        <v>199</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>159</v>
       </c>
       <c r="D119" s="6">
+        <v>0.77</v>
+      </c>
+      <c r="M119" s="4"/>
+    </row>
+    <row r="120" spans="1:13">
+      <c r="A120" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="B120" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="D120" s="6">
         <v>0.68</v>
       </c>
-      <c r="M119" s="4"/>
-    </row>
-    <row r="120" spans="1:13">
-      <c r="A120" s="5" t="s">
+      <c r="M120" s="4"/>
+    </row>
+    <row r="121" spans="1:13">
+      <c r="A121" s="5" t="s">
         <v>454</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B121" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="C120" s="5" t="s">
+      <c r="C121" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="D120" s="5">
+      <c r="D121" s="5">
         <v>0</v>
       </c>
-      <c r="J120">
+      <c r="J121">
         <v>0.86</v>
-      </c>
-      <c r="M120" s="4"/>
-    </row>
-    <row r="121" spans="1:13">
-      <c r="A121" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="B121" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="C121" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D121" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="J121">
-        <v>0.8</v>
       </c>
       <c r="M121" s="4"/>
     </row>
     <row r="122" spans="1:13">
       <c r="A122" s="6" t="s">
-        <v>270</v>
+        <v>304</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>271</v>
+        <v>305</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D122" s="6">
-        <v>0.86</v>
+        <v>0.87</v>
+      </c>
+      <c r="J122">
+        <v>0.8</v>
       </c>
       <c r="M122" s="4"/>
     </row>
     <row r="123" spans="1:13">
       <c r="A123" s="6" t="s">
-        <v>312</v>
+        <v>270</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>313</v>
+        <v>271</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D123" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M123" s="4"/>
     </row>
     <row r="124" spans="1:13">
       <c r="A124" s="6" t="s">
-        <v>334</v>
+        <v>312</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>335</v>
+        <v>313</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D124" s="6">
-        <v>0.64</v>
+        <v>0.79</v>
       </c>
       <c r="M124" s="4"/>
     </row>
     <row r="125" spans="1:13">
       <c r="A125" s="6" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B125" s="6" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="C125" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D125" s="6">
-        <v>0.79</v>
+        <v>0.64</v>
       </c>
       <c r="M125" s="4"/>
     </row>
     <row r="126" spans="1:13">
       <c r="A126" s="6" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D126" s="6">
-        <v>0.69</v>
+        <v>0.79</v>
       </c>
       <c r="M126" s="4"/>
     </row>
     <row r="127" spans="1:13">
       <c r="A127" s="6" t="s">
-        <v>258</v>
+        <v>336</v>
       </c>
       <c r="B127" s="6" t="s">
-        <v>259</v>
+        <v>337</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D127" s="6">
-        <v>0.91</v>
+        <v>0.69</v>
       </c>
       <c r="M127" s="4"/>
     </row>
     <row r="128" spans="1:13">
       <c r="A128" s="6" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D128" s="6">
-        <v>0.88</v>
+        <v>0.91</v>
       </c>
       <c r="M128" s="4"/>
     </row>
     <row r="129" spans="1:13">
       <c r="A129" s="6" t="s">
-        <v>306</v>
+        <v>266</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>307</v>
+        <v>267</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D129" s="6">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="M129" s="4"/>
     </row>
     <row r="130" spans="1:13">
       <c r="A130" s="6" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D130" s="6">
-        <v>0.87</v>
-      </c>
-      <c r="J130">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="M130" s="4"/>
     </row>
     <row r="131" spans="1:13">
       <c r="A131" s="6" t="s">
-        <v>326</v>
+        <v>290</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>327</v>
+        <v>291</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D131" s="6">
+        <v>0.87</v>
+      </c>
+      <c r="J131">
         <v>0.8</v>
       </c>
       <c r="M131" s="4"/>
     </row>
     <row r="132" spans="1:13">
       <c r="A132" s="6" t="s">
-        <v>340</v>
+        <v>326</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D132" s="6">
-        <v>0.41</v>
+        <v>0.8</v>
       </c>
       <c r="M132" s="4"/>
     </row>
     <row r="133" spans="1:13">
       <c r="A133" s="6" t="s">
-        <v>284</v>
+        <v>340</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>285</v>
+        <v>341</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D133" s="6">
-        <v>0.81</v>
+        <v>0.41</v>
       </c>
       <c r="M133" s="4"/>
     </row>
     <row r="134" spans="1:13">
       <c r="A134" s="6" t="s">
-        <v>260</v>
+        <v>284</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>261</v>
+        <v>285</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D134" s="6">
-        <v>0.71</v>
+        <v>0.81</v>
       </c>
       <c r="M134" s="4"/>
     </row>
     <row r="135" spans="1:13">
       <c r="A135" s="6" t="s">
-        <v>274</v>
+        <v>260</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>275</v>
+        <v>261</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D135" s="6">
+        <v>0.71</v>
+      </c>
+      <c r="M135" s="4"/>
+    </row>
+    <row r="136" spans="1:13">
+      <c r="A136" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B136" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>245</v>
+      </c>
+      <c r="D136" s="6">
         <v>0.86</v>
       </c>
-      <c r="M135" s="4"/>
-    </row>
-    <row r="136" spans="1:13">
-      <c r="A136" s="5" t="s">
+      <c r="M136" s="4"/>
+    </row>
+    <row r="137" spans="1:13">
+      <c r="A137" s="5" t="s">
         <v>458</v>
       </c>
-      <c r="B136" s="5" t="s">
+      <c r="B137" s="5" t="s">
         <v>459</v>
       </c>
-      <c r="C136" s="5" t="s">
+      <c r="C137" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="D136" s="5">
+      <c r="D137" s="5">
         <v>0</v>
       </c>
-      <c r="J136">
+      <c r="J137">
         <v>0.83</v>
-      </c>
-      <c r="M136" s="4"/>
-    </row>
-    <row r="137" spans="1:13">
-      <c r="A137" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="B137" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="D137" s="6">
-        <v>0.87</v>
       </c>
       <c r="M137" s="4"/>
     </row>
     <row r="138" spans="1:13">
       <c r="A138" s="6" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D138" s="6">
-        <v>0.8</v>
+        <v>0.87</v>
       </c>
       <c r="M138" s="4"/>
     </row>
     <row r="139" spans="1:13">
       <c r="A139" s="6" t="s">
-        <v>288</v>
+        <v>310</v>
       </c>
       <c r="B139" s="6" t="s">
-        <v>289</v>
+        <v>311</v>
       </c>
       <c r="C139" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D139" s="6">
-        <v>0.88</v>
+        <v>0.8</v>
       </c>
       <c r="M139" s="4"/>
     </row>
     <row r="140" spans="1:13">
       <c r="A140" s="6" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="C140" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D140" s="6">
-        <v>0.98</v>
+        <v>0.88</v>
       </c>
       <c r="M140" s="4"/>
     </row>
     <row r="141" spans="1:13">
       <c r="A141" s="6" t="s">
-        <v>308</v>
+        <v>338</v>
       </c>
       <c r="B141" s="6" t="s">
-        <v>309</v>
+        <v>339</v>
       </c>
       <c r="C141" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D141" s="6">
-        <v>0.75</v>
+        <v>0.98</v>
       </c>
       <c r="M141" s="4"/>
     </row>
     <row r="142" spans="1:13">
       <c r="A142" s="6" t="s">
-        <v>330</v>
+        <v>308</v>
       </c>
       <c r="B142" s="6" t="s">
-        <v>331</v>
+        <v>309</v>
       </c>
       <c r="C142" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D142" s="6">
-        <v>0.85</v>
+        <v>0.75</v>
       </c>
       <c r="M142" s="4"/>
     </row>
     <row r="143" spans="1:13">
       <c r="A143" s="6" t="s">
-        <v>246</v>
+        <v>330</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>247</v>
+        <v>331</v>
       </c>
       <c r="C143" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D143" s="6">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="M143" s="4"/>
     </row>
     <row r="144" spans="1:13">
       <c r="A144" s="6" t="s">
-        <v>324</v>
+        <v>246</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>325</v>
+        <v>247</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D144" s="6">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="M144" s="4"/>
     </row>
     <row r="145" spans="1:13">
       <c r="A145" s="6" t="s">
-        <v>262</v>
+        <v>324</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>263</v>
+        <v>325</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D145" s="6">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="M145" s="4"/>
     </row>
     <row r="146" spans="1:13">
       <c r="A146" s="6" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D146" s="6">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="M146" s="4"/>
     </row>
     <row r="147" spans="1:13">
       <c r="A147" s="6" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D147" s="6">
-        <v>0.88</v>
-      </c>
-      <c r="J147">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="M147" s="4"/>
     </row>
     <row r="148" spans="1:13">
       <c r="A148" s="6" t="s">
-        <v>294</v>
+        <v>314</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>295</v>
+        <v>315</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D148" s="6">
-        <v>0.8</v>
+        <v>0.88</v>
+      </c>
+      <c r="J148">
+        <v>0.83</v>
       </c>
       <c r="M148" s="4"/>
     </row>
     <row r="149" spans="1:13">
       <c r="A149" s="6" t="s">
-        <v>272</v>
+        <v>294</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>273</v>
+        <v>295</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D149" s="6">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="M149" s="4"/>
     </row>
     <row r="150" spans="1:13">
       <c r="A150" s="6" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D150" s="6">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="M150" s="4"/>
     </row>
     <row r="151" spans="1:13">
       <c r="A151" s="6" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D151" s="6">
-        <v>0.81</v>
+        <v>1</v>
       </c>
       <c r="M151" s="4"/>
     </row>
     <row r="152" spans="1:13">
       <c r="A152" s="6" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D152" s="6">
-        <v>0.84</v>
+        <v>0.81</v>
       </c>
       <c r="M152" s="4"/>
     </row>
     <row r="153" spans="1:13">
       <c r="A153" s="6" t="s">
-        <v>286</v>
+        <v>254</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D153" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J153">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="M153" s="4"/>
     </row>
     <row r="154" spans="1:13">
       <c r="A154" s="6" t="s">
-        <v>252</v>
+        <v>286</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>253</v>
+        <v>287</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D154" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
+      </c>
+      <c r="J154">
+        <v>0.83</v>
       </c>
       <c r="M154" s="4"/>
     </row>
     <row r="155" spans="1:13">
       <c r="A155" s="6" t="s">
-        <v>298</v>
+        <v>252</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>299</v>
+        <v>253</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D155" s="6">
-        <v>0.91</v>
+        <v>0.85</v>
       </c>
       <c r="M155" s="4"/>
     </row>
     <row r="156" spans="1:13">
       <c r="A156" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D156" s="6">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="M156" s="4"/>
     </row>
     <row r="157" spans="1:13">
       <c r="A157" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D157" s="6">
-        <v>0.79</v>
+        <v>0.86</v>
       </c>
       <c r="M157" s="4"/>
     </row>
     <row r="158" spans="1:13">
       <c r="A158" s="6" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D158" s="6">
-        <v>0.86</v>
+        <v>0.79</v>
       </c>
       <c r="M158" s="4"/>
     </row>
     <row r="159" spans="1:13">
       <c r="A159" s="6" t="s">
-        <v>300</v>
+        <v>243</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>301</v>
+        <v>244</v>
       </c>
       <c r="C159" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D159" s="6">
-        <v>0.75</v>
+        <v>0.86</v>
       </c>
       <c r="M159" s="4"/>
     </row>
     <row r="160" spans="1:13">
       <c r="A160" s="6" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>249</v>
+        <v>301</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D160" s="6">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M160" s="4"/>
     </row>
     <row r="161" spans="1:13">
       <c r="A161" s="6" t="s">
-        <v>332</v>
+        <v>248</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>333</v>
+        <v>249</v>
       </c>
       <c r="C161" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D161" s="6">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="M161" s="4"/>
     </row>
     <row r="162" spans="1:13">
       <c r="A162" s="6" t="s">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>293</v>
+        <v>333</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D162" s="6">
-        <v>0.93</v>
+        <v>0.86</v>
       </c>
       <c r="M162" s="4"/>
     </row>
     <row r="163" spans="1:13">
       <c r="A163" s="6" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D163" s="6">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="M163" s="4"/>
     </row>
     <row r="164" spans="1:13">
       <c r="A164" s="6" t="s">
-        <v>256</v>
+        <v>278</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>257</v>
+        <v>279</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D164" s="6">
-        <v>0.91</v>
-      </c>
-      <c r="J164">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M164" s="4"/>
     </row>
     <row r="165" spans="1:13">
       <c r="A165" s="6" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="B165" s="6" t="s">
-        <v>277</v>
+        <v>257</v>
       </c>
       <c r="C165" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D165" s="6">
-        <v>0.81</v>
+        <v>0.91</v>
+      </c>
+      <c r="J165">
+        <v>0.8</v>
       </c>
       <c r="M165" s="4"/>
     </row>
     <row r="166" spans="1:13">
       <c r="A166" s="6" t="s">
-        <v>250</v>
+        <v>276</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>251</v>
+        <v>277</v>
       </c>
       <c r="C166" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D166" s="6">
-        <v>0.93</v>
+        <v>0.81</v>
       </c>
       <c r="M166" s="4"/>
     </row>
     <row r="167" spans="1:13">
       <c r="A167" s="6" t="s">
-        <v>320</v>
+        <v>250</v>
       </c>
       <c r="B167" s="6" t="s">
-        <v>321</v>
+        <v>251</v>
       </c>
       <c r="C167" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D167" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J167">
-        <v>0.83</v>
+        <v>0.93</v>
       </c>
       <c r="M167" s="4"/>
     </row>
     <row r="168" spans="1:13">
       <c r="A168" s="6" t="s">
-        <v>282</v>
+        <v>320</v>
       </c>
       <c r="B168" s="6" t="s">
-        <v>283</v>
+        <v>321</v>
       </c>
       <c r="C168" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D168" s="6">
-        <v>0.8</v>
+        <v>0.81</v>
+      </c>
+      <c r="J168">
+        <v>0.83</v>
       </c>
       <c r="M168" s="4"/>
     </row>
     <row r="169" spans="1:13">
       <c r="A169" s="6" t="s">
-        <v>322</v>
+        <v>282</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>323</v>
+        <v>283</v>
       </c>
       <c r="C169" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D169" s="6">
-        <v>0.85</v>
+        <v>0.8</v>
       </c>
       <c r="M169" s="4"/>
     </row>
     <row r="170" spans="1:13">
       <c r="A170" s="6" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="C170" s="6" t="s">
         <v>245</v>
       </c>
       <c r="D170" s="6">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="M170" s="4"/>
     </row>
     <row r="171" spans="1:13">
       <c r="A171" s="6" t="s">
-        <v>349</v>
+        <v>318</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>350</v>
+        <v>319</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>344</v>
+        <v>245</v>
       </c>
       <c r="D171" s="6">
-        <v>0.77</v>
+        <v>0.89</v>
       </c>
       <c r="M171" s="4"/>
     </row>
     <row r="172" spans="1:13">
       <c r="A172" s="6" t="s">
-        <v>393</v>
+        <v>349</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>394</v>
+        <v>350</v>
       </c>
       <c r="C172" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D172" s="6">
-        <v>0.8</v>
+        <v>0.77</v>
       </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
       <c r="A173" s="6" t="s">
-        <v>431</v>
+        <v>393</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>432</v>
+        <v>394</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D173" s="6">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
       <c r="A174" s="6" t="s">
-        <v>365</v>
+        <v>431</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>366</v>
+        <v>432</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D174" s="6">
-        <v>0.82</v>
+        <v>0.74</v>
       </c>
       <c r="M174" s="4"/>
     </row>
     <row r="175" spans="1:13">
       <c r="A175" s="6" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D175" s="6">
-        <v>0.85</v>
+        <v>0.82</v>
       </c>
       <c r="M175" s="4"/>
     </row>
     <row r="176" spans="1:13">
       <c r="A176" s="6" t="s">
-        <v>373</v>
+        <v>351</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>374</v>
+        <v>352</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D176" s="6">
-        <v>0.98</v>
+        <v>0.85</v>
       </c>
       <c r="M176" s="4"/>
     </row>
     <row r="177" spans="1:13">
       <c r="A177" s="6" t="s">
-        <v>435</v>
+        <v>373</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>436</v>
+        <v>374</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D177" s="6">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="M177" s="4"/>
     </row>
     <row r="178" spans="1:13">
       <c r="A178" s="6" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D178" s="6">
-        <v>0.67</v>
+        <v>0.93</v>
       </c>
       <c r="M178" s="4"/>
     </row>
     <row r="179" spans="1:13">
       <c r="A179" s="6" t="s">
-        <v>419</v>
+        <v>437</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>420</v>
+        <v>438</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D179" s="6">
-        <v>0.96</v>
+        <v>0.67</v>
       </c>
       <c r="M179" s="4"/>
     </row>
     <row r="180" spans="1:13">
       <c r="A180" s="6" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D180" s="6">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="M180" s="4"/>
     </row>
     <row r="181" spans="1:13">
       <c r="A181" s="6" t="s">
-        <v>377</v>
+        <v>413</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>378</v>
+        <v>414</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D181" s="6">
-        <v>0.84</v>
+        <v>0.92</v>
       </c>
       <c r="M181" s="4"/>
     </row>
     <row r="182" spans="1:13">
       <c r="A182" s="6" t="s">
-        <v>395</v>
+        <v>377</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>396</v>
+        <v>378</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D182" s="6">
-        <v>0.63</v>
+        <v>0.84</v>
       </c>
       <c r="M182" s="4"/>
     </row>
     <row r="183" spans="1:13">
       <c r="A183" s="6" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D183" s="6">
-        <v>0.82</v>
+        <v>0.63</v>
       </c>
       <c r="M183" s="4"/>
     </row>
     <row r="184" spans="1:13">
       <c r="A184" s="6" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D184" s="6">
-        <v>0.93</v>
+        <v>0.82</v>
       </c>
       <c r="M184" s="4"/>
     </row>
     <row r="185" spans="1:13">
       <c r="A185" s="6" t="s">
-        <v>415</v>
+        <v>397</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>416</v>
+        <v>398</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D185" s="6">
-        <v>0.75</v>
+        <v>0.93</v>
       </c>
       <c r="M185" s="4"/>
     </row>
     <row r="186" spans="1:13">
       <c r="A186" s="6" t="s">
-        <v>361</v>
+        <v>415</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>362</v>
+        <v>416</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D186" s="6">
-        <v>0.96</v>
+        <v>0.75</v>
       </c>
       <c r="M186" s="4"/>
     </row>
     <row r="187" spans="1:13">
       <c r="A187" s="6" t="s">
-        <v>427</v>
+        <v>361</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>428</v>
+        <v>362</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D187" s="6">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
       <c r="A188" s="6" t="s">
-        <v>367</v>
+        <v>427</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D188" s="6">
-        <v>0.81</v>
+        <v>0.92</v>
       </c>
       <c r="M188" s="4"/>
     </row>
     <row r="189" spans="1:13">
       <c r="A189" s="6" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D189" s="6">
-        <v>0.9</v>
+        <v>0.81</v>
       </c>
       <c r="M189" s="4"/>
     </row>
     <row r="190" spans="1:13">
       <c r="A190" s="6" t="s">
-        <v>405</v>
+        <v>381</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>406</v>
+        <v>382</v>
       </c>
       <c r="C190" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D190" s="6">
-        <v>0.96</v>
+        <v>0.9</v>
       </c>
       <c r="M190" s="4"/>
     </row>
     <row r="191" spans="1:13">
       <c r="A191" s="6" t="s">
-        <v>342</v>
+        <v>405</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>343</v>
+        <v>406</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D191" s="6">
-        <v>0.76</v>
+        <v>0.96</v>
       </c>
       <c r="M191" s="4"/>
     </row>
     <row r="192" spans="1:13">
       <c r="A192" s="6" t="s">
-        <v>407</v>
+        <v>342</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>408</v>
+        <v>343</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D192" s="6">
-        <v>0.93</v>
+        <v>0.76</v>
       </c>
       <c r="M192" s="4"/>
     </row>
     <row r="193" spans="1:13">
       <c r="A193" s="6" t="s">
-        <v>371</v>
+        <v>407</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>372</v>
+        <v>408</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D193" s="6">
-        <v>0.79</v>
+        <v>0.93</v>
       </c>
       <c r="M193" s="4"/>
     </row>
     <row r="194" spans="1:13">
       <c r="A194" s="6" t="s">
-        <v>447</v>
+        <v>371</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>448</v>
+        <v>372</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D194" s="6">
-        <v>0.81</v>
+        <v>0.79</v>
       </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
       <c r="A195" s="6" t="s">
-        <v>369</v>
+        <v>447</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>370</v>
+        <v>448</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D195" s="6">
-        <v>0.85</v>
+        <v>0.81</v>
       </c>
       <c r="M195" s="4"/>
     </row>
     <row r="196" spans="1:13">
       <c r="A196" s="6" t="s">
-        <v>411</v>
+        <v>369</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>412</v>
+        <v>370</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D196" s="6">
-        <v>0.96</v>
+        <v>0.85</v>
       </c>
       <c r="M196" s="4"/>
     </row>
     <row r="197" spans="1:13">
       <c r="A197" s="6" t="s">
-        <v>345</v>
+        <v>411</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>346</v>
+        <v>412</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D197" s="6">
-        <v>0.81</v>
-      </c>
-      <c r="J197">
-        <v>0.79</v>
+        <v>0.96</v>
       </c>
       <c r="M197" s="4"/>
     </row>
     <row r="198" spans="1:13">
       <c r="A198" s="6" t="s">
-        <v>399</v>
+        <v>345</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>400</v>
+        <v>346</v>
       </c>
       <c r="C198" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D198" s="6">
-        <v>0.96</v>
+        <v>0.81</v>
+      </c>
+      <c r="J198">
+        <v>0.79</v>
       </c>
       <c r="M198" s="4"/>
     </row>
     <row r="199" spans="1:13">
       <c r="A199" s="6" t="s">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>376</v>
+        <v>400</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D199" s="6">
-        <v>0.85</v>
+        <v>0.96</v>
       </c>
       <c r="M199" s="4"/>
     </row>
     <row r="200" spans="1:13">
       <c r="A200" s="6" t="s">
-        <v>389</v>
+        <v>375</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>390</v>
+        <v>376</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D200" s="6">
-        <v>0.77</v>
+        <v>0.85</v>
       </c>
       <c r="M200" s="4"/>
     </row>
     <row r="201" spans="1:13">
       <c r="A201" s="6" t="s">
-        <v>409</v>
+        <v>389</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>410</v>
+        <v>390</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D201" s="6">
-        <v>0.93</v>
+        <v>0.77</v>
       </c>
       <c r="M201" s="4"/>
     </row>
     <row r="202" spans="1:13">
       <c r="A202" s="6" t="s">
-        <v>421</v>
+        <v>409</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D202" s="6">
-        <v>1</v>
-      </c>
-      <c r="J202">
         <v>0.93</v>
       </c>
       <c r="M202" s="4"/>
     </row>
     <row r="203" spans="1:13">
       <c r="A203" s="6" t="s">
-        <v>433</v>
+        <v>421</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>434</v>
+        <v>422</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D203" s="6">
-        <v>0.91</v>
+        <v>1</v>
+      </c>
+      <c r="J203">
+        <v>0.93</v>
       </c>
       <c r="M203" s="4"/>
     </row>
     <row r="204" spans="1:13">
       <c r="A204" s="6" t="s">
-        <v>357</v>
+        <v>433</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>358</v>
+        <v>434</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D204" s="6">
-        <v>0.55000000000000004</v>
+        <v>0.91</v>
       </c>
       <c r="M204" s="4"/>
     </row>
     <row r="205" spans="1:13">
       <c r="A205" s="6" t="s">
-        <v>417</v>
+        <v>357</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>418</v>
+        <v>358</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D205" s="6">
-        <v>0.89</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="M205" s="4"/>
     </row>
     <row r="206" spans="1:13">
       <c r="A206" s="6" t="s">
-        <v>439</v>
+        <v>417</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>440</v>
+        <v>418</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D206" s="6">
+        <v>0.89</v>
+      </c>
+      <c r="M206" s="4"/>
+    </row>
+    <row r="207" spans="1:13">
+      <c r="A207" s="6" t="s">
+        <v>439</v>
+      </c>
+      <c r="B207" s="6" t="s">
+        <v>440</v>
+      </c>
+      <c r="C207" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D207" s="6">
         <v>0.98</v>
       </c>
-      <c r="M206" s="4"/>
-    </row>
-    <row r="207" spans="1:13">
-      <c r="A207" s="5" t="s">
+      <c r="M207" s="4"/>
+    </row>
+    <row r="208" spans="1:13">
+      <c r="A208" s="5" t="s">
         <v>449</v>
       </c>
-      <c r="B207" s="5" t="s">
+      <c r="B208" s="5" t="s">
         <v>450</v>
       </c>
-      <c r="C207" s="5" t="s">
+      <c r="C208" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="D207" s="5">
+      <c r="D208" s="5">
         <v>0</v>
       </c>
-      <c r="J207">
+      <c r="J208">
         <v>0.93</v>
-      </c>
-      <c r="M207" s="4"/>
-    </row>
-    <row r="208" spans="1:13">
-      <c r="A208" s="6" t="s">
-        <v>387</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>388</v>
-      </c>
-      <c r="C208" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="D208" s="6">
-        <v>0.98</v>
       </c>
       <c r="M208" s="4"/>
     </row>
     <row r="209" spans="1:13">
       <c r="A209" s="6" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D209" s="6">
-        <v>0.96</v>
+        <v>0.98</v>
       </c>
       <c r="M209" s="4"/>
     </row>
     <row r="210" spans="1:13">
       <c r="A210" s="6" t="s">
-        <v>383</v>
+        <v>403</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>344</v>
@@ -5232,151 +5268,151 @@
     </row>
     <row r="211" spans="1:13">
       <c r="A211" s="6" t="s">
-        <v>425</v>
+        <v>383</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>426</v>
+        <v>384</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D211" s="6">
-        <v>0.42</v>
-      </c>
-      <c r="J211">
-        <v>0.93</v>
+        <v>0.96</v>
       </c>
       <c r="M211" s="4"/>
     </row>
     <row r="212" spans="1:13">
       <c r="A212" s="6" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D212" s="6">
-        <v>0.88</v>
+        <v>0.42</v>
+      </c>
+      <c r="J212">
+        <v>0.93</v>
       </c>
       <c r="M212" s="4"/>
     </row>
     <row r="213" spans="1:13">
       <c r="A213" s="6" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D213" s="6">
-        <v>0.78</v>
-      </c>
-      <c r="J213">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="M213" s="4"/>
     </row>
     <row r="214" spans="1:13">
       <c r="A214" s="6" t="s">
-        <v>363</v>
+        <v>445</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>364</v>
+        <v>446</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D214" s="6">
-        <v>0.96</v>
+        <v>0.78</v>
+      </c>
+      <c r="J214">
+        <v>0.93</v>
       </c>
       <c r="M214" s="4"/>
     </row>
     <row r="215" spans="1:13">
       <c r="A215" s="6" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D215" s="6">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
       <c r="M215" s="4"/>
     </row>
     <row r="216" spans="1:13">
       <c r="A216" s="6" t="s">
-        <v>391</v>
+        <v>353</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>392</v>
+        <v>354</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D216" s="6">
-        <v>0.76</v>
+        <v>0.68</v>
       </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
       <c r="A217" s="6" t="s">
-        <v>429</v>
+        <v>391</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>430</v>
+        <v>392</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D217" s="6">
-        <v>0.41</v>
+        <v>0.76</v>
       </c>
       <c r="M217" s="4"/>
     </row>
     <row r="218" spans="1:13">
       <c r="A218" s="6" t="s">
-        <v>347</v>
+        <v>429</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>348</v>
+        <v>430</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D218" s="6">
-        <v>0.8</v>
+        <v>0.41</v>
       </c>
       <c r="M218" s="4"/>
     </row>
     <row r="219" spans="1:13">
       <c r="A219" s="6" t="s">
-        <v>379</v>
+        <v>347</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>380</v>
+        <v>348</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D219" s="6">
-        <v>0.91</v>
+        <v>0.8</v>
       </c>
       <c r="M219" s="4"/>
     </row>
     <row r="220" spans="1:13">
       <c r="A220" s="6" t="s">
-        <v>423</v>
+        <v>379</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>424</v>
+        <v>380</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>344</v>
@@ -5388,43 +5424,43 @@
     </row>
     <row r="221" spans="1:13">
       <c r="A221" s="6" t="s">
-        <v>359</v>
+        <v>423</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>360</v>
+        <v>424</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D221" s="6">
-        <v>0.95</v>
-      </c>
-      <c r="J221">
-        <v>0.83</v>
+        <v>0.91</v>
       </c>
       <c r="M221" s="4"/>
     </row>
     <row r="222" spans="1:13">
       <c r="A222" s="6" t="s">
-        <v>385</v>
+        <v>359</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>386</v>
+        <v>360</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D222" s="6">
-        <v>0.97</v>
+        <v>0.95</v>
+      </c>
+      <c r="J222">
+        <v>0.83</v>
       </c>
       <c r="M222" s="4"/>
     </row>
     <row r="223" spans="1:13">
       <c r="A223" s="6" t="s">
-        <v>355</v>
+        <v>385</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>356</v>
+        <v>386</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>344</v>
@@ -5436,27 +5472,35 @@
     </row>
     <row r="224" spans="1:13">
       <c r="A224" s="6" t="s">
-        <v>443</v>
+        <v>355</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>444</v>
+        <v>356</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>344</v>
       </c>
       <c r="D224" s="6">
+        <v>0.97</v>
+      </c>
+      <c r="M224" s="4"/>
+    </row>
+    <row r="225" spans="1:13">
+      <c r="A225" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="B225" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C225" s="6" t="s">
+        <v>344</v>
+      </c>
+      <c r="D225" s="6">
         <v>0.88</v>
       </c>
-      <c r="J224">
+      <c r="J225">
         <v>0.93</v>
       </c>
-      <c r="M224" s="4"/>
-    </row>
-    <row r="225" spans="1:13">
-      <c r="A225" s="5"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="5"/>
-      <c r="D225" s="5"/>
       <c r="M225" s="4"/>
     </row>
     <row r="226" spans="1:13">

--- a/cw11042026.xlsx
+++ b/cw11042026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/trevor/Documents/GitHub/course/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E851313-6201-9249-9F5C-94CC154F5682}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4800055C-8A5E-1A49-95E3-C7F361278D1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="880" yWindow="620" windowWidth="29360" windowHeight="16060" xr2:uid="{EC16AC82-7674-0540-BCFF-830B59CE68F0}"/>
   </bookViews>
@@ -4685,6 +4685,9 @@
       <c r="D172" s="6">
         <v>0.77</v>
       </c>
+      <c r="J172">
+        <v>0.8</v>
+      </c>
       <c r="M172" s="4"/>
     </row>
     <row r="173" spans="1:13">
@@ -4700,6 +4703,9 @@
       <c r="D173" s="6">
         <v>0.8</v>
       </c>
+      <c r="J173">
+        <v>0.85</v>
+      </c>
       <c r="M173" s="4"/>
     </row>
     <row r="174" spans="1:13">
@@ -4745,6 +4751,9 @@
       <c r="D176" s="6">
         <v>0.85</v>
       </c>
+      <c r="J176">
+        <v>0.8</v>
+      </c>
       <c r="M176" s="4"/>
     </row>
     <row r="177" spans="1:13">
@@ -4910,6 +4919,9 @@
       <c r="D187" s="6">
         <v>0.96</v>
       </c>
+      <c r="J187">
+        <v>0.8</v>
+      </c>
       <c r="M187" s="4"/>
     </row>
     <row r="188" spans="1:13">
@@ -5015,6 +5027,9 @@
       <c r="D194" s="6">
         <v>0.79</v>
       </c>
+      <c r="J194">
+        <v>0.85</v>
+      </c>
       <c r="M194" s="4"/>
     </row>
     <row r="195" spans="1:13">
@@ -5216,6 +5231,9 @@
       <c r="D207" s="6">
         <v>0.98</v>
       </c>
+      <c r="J207">
+        <v>0.85</v>
+      </c>
       <c r="M207" s="4"/>
     </row>
     <row r="208" spans="1:13">
@@ -5360,6 +5378,9 @@
       <c r="D216" s="6">
         <v>0.68</v>
       </c>
+      <c r="J216">
+        <v>0.8</v>
+      </c>
       <c r="M216" s="4"/>
     </row>
     <row r="217" spans="1:13">
@@ -5467,6 +5488,9 @@
       </c>
       <c r="D223" s="6">
         <v>0.97</v>
+      </c>
+      <c r="J223">
+        <v>0.8</v>
       </c>
       <c r="M223" s="4"/>
     </row>
